--- a/Sajjad data/by_country_and_state/USA/MN.xlsx
+++ b/Sajjad data/by_country_and_state/USA/MN.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="156" uniqueCount="86">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="871" uniqueCount="402">
   <si>
     <t>Business Name</t>
   </si>
@@ -269,6 +269,954 @@
   </si>
   <si>
     <t>2026-10-25T04:20:21.112Z</t>
+  </si>
+  <si>
+    <t>Donald E. Lareau, DDS, MS</t>
+  </si>
+  <si>
+    <t>(952) 830-1311</t>
+  </si>
+  <si>
+    <t>3555 Louisiana Ave S, St Louis Park, MN 55426</t>
+  </si>
+  <si>
+    <t>St Louis Park</t>
+  </si>
+  <si>
+    <t>SundayClosed</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/Donald+E.+Lareau,+DDS,+MS/data=!4m7!3m6!1s0x87f6241ac04767bd:0x10739794512e956e!8m2!3d44.9394461!4d-93.3692577!16s%2Fg%2F1tj5r90m!19sChIJvWdHwBok9ocRbpUuUZSXcxA?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>2026-10-25T08:59:38.361Z</t>
+  </si>
+  <si>
+    <t>Dr. Dan B. Ang</t>
+  </si>
+  <si>
+    <t>(763) 542-8723</t>
+  </si>
+  <si>
+    <t>Endodontist</t>
+  </si>
+  <si>
+    <t>5851 Duluth St #313, Minneapolis, MN 55422</t>
+  </si>
+  <si>
+    <t>3.8</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/Dr.+Dan+B.+Ang/data=!4m7!3m6!1s0x52b3346fe2410077:0x41d1df608de87c58!8m2!3d44.9986107!4d-93.3548977!16s%2Fg%2F11b7q93l3h!19sChIJdwBB4m80s1IRWHzojWDf0UE?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>2026-10-25T08:59:42.183Z</t>
+  </si>
+  <si>
+    <t>West Side Dental Clinic</t>
+  </si>
+  <si>
+    <t>(844) 207-4572</t>
+  </si>
+  <si>
+    <t>478 S Robert St, St Paul, MN 55107</t>
+  </si>
+  <si>
+    <t>St Paul</t>
+  </si>
+  <si>
+    <t>2.8</t>
+  </si>
+  <si>
+    <t>Sunday7 AM–7 PM</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/West+Side+Dental+Clinic/data=!4m7!3m6!1s0x87f7d522b00b2905:0x7163b4aea81d3614!8m2!3d44.9317118!4d-93.08055!16s%2Fg%2F1tfx5g47!19sChIJBSkLsCLV94cRFDYdqK60Y3E?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>2026-10-25T08:59:58.058Z</t>
+  </si>
+  <si>
+    <t>Maplewood Family Dentistry</t>
+  </si>
+  <si>
+    <t>(651) 842-8915</t>
+  </si>
+  <si>
+    <t>2480 White Bear Ave, Maplewood, MN 55109</t>
+  </si>
+  <si>
+    <t>Maplewood</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/Maplewood+Family+Dentistry/data=!4m7!3m6!1s0x52b2d35a4525eabb:0xa78ab6a26cf985cd!8m2!3d45.0162244!4d-93.0191312!16s%2Fg%2F11zbnjb07s!19sChIJu-olRVrTslIRzYX5bKK2iqc?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>2026-10-25T09:00:24.282Z</t>
+  </si>
+  <si>
+    <t>Childrens Dental Clinc: Moeller Mark DDS</t>
+  </si>
+  <si>
+    <t>(651) 760-8040</t>
+  </si>
+  <si>
+    <t>St Paul, MN 55106</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/Childrens+Dental+Clinc:+Moeller+Mark+DDS/data=!4m7!3m6!1s0x52b2d4daaaaaaaab:0xa0dbaedd193893e!8m2!3d44.9687549!4d-93.0485951!16s%2Fg%2F1v2gdd9b!19sChIJq6qqqtrUslIRPomT0e26DQo?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>2026-10-25T09:02:11.850Z</t>
+  </si>
+  <si>
+    <t>Great Lakes Implant Institute</t>
+  </si>
+  <si>
+    <t>(763) 417-9975</t>
+  </si>
+  <si>
+    <t>Dental school</t>
+  </si>
+  <si>
+    <t>Wells Fargo Place, 30 E 7th St #101, St Paul, MN 55101</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/Great+Lakes+Implant+Institute/data=!4m7!3m6!1s0x87f7d54d714c190f:0xc7a399b996c0b117!8m2!3d44.9479563!4d-93.0953433!16s%2Fg%2F11c0r5zrbp!19sChIJDxlMcU3V94cRF7HAlrmZo8c?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>2026-10-25T09:02:37.090Z</t>
+  </si>
+  <si>
+    <t>Emergency Dental Source</t>
+  </si>
+  <si>
+    <t>(651) 362-9546</t>
+  </si>
+  <si>
+    <t>Emergency dental service</t>
+  </si>
+  <si>
+    <t>1991 Ford Pkwy ste 200, St Paul, MN 55116</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/Emergency+Dental+Source/data=!4m7!3m6!1s0x87f629b6a43b66a3:0x989f2a8408701d54!8m2!3d44.9183076!4d-93.1841918!16s%2Fg%2F11zxx6w8dy!19sChIJo2Y7pLYp9ocRVB1wCIQqn5g?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>2026-10-25T09:02:52.579Z</t>
+  </si>
+  <si>
+    <t>Saint Paul Immediate Dentistry</t>
+  </si>
+  <si>
+    <t>(651) 376-6909</t>
+  </si>
+  <si>
+    <t>905 Iroquois Ave, St Paul, MN 55119</t>
+  </si>
+  <si>
+    <t>4.1</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/Saint+Paul+Immediate+Dentistry/data=!4m7!3m6!1s0x52b2d38c08c9e79d:0x8d543f70960266cc!8m2!3d44.9686163!4d-93.0166887!16s%2Fg%2F11p06d3nwk!19sChIJnefJCIzTslIRzGYClnA_VI0?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>2026-10-25T09:02:54.602Z</t>
+  </si>
+  <si>
+    <t>Immediate Dental Roseville</t>
+  </si>
+  <si>
+    <t>(651) 571-7998</t>
+  </si>
+  <si>
+    <t>1233 Larpenteur Ave W, Roseville, MN 55113</t>
+  </si>
+  <si>
+    <t>Roseville</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/Immediate+Dental+Roseville/data=!4m7!3m6!1s0x52b32b3b1a20f221:0x8f5cd9504d73d56c!8m2!3d44.9923609!4d-93.152312!16s%2Fg%2F11vzgkd1mt!19sChIJIfIgGjsrs1IRbNVzTVDZXI8?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>2026-10-25T09:02:56.847Z</t>
+  </si>
+  <si>
+    <t>Afton Road Dental Associates</t>
+  </si>
+  <si>
+    <t>(651) 739-5110</t>
+  </si>
+  <si>
+    <t>2716 Upper Afton Rd, St Paul, MN 55119</t>
+  </si>
+  <si>
+    <t>2.7</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/Afton+Road+Dental+Associates/data=!4m7!3m6!1s0x87f7d648379db829:0xbf8d4dfcd4ca314e!8m2!3d44.9411566!4d-92.9855685!16s%2Fg%2F1td2n12d!19sChIJKbidN0jW94cRTjHK1PxNjb8?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>2026-10-25T09:03:22.448Z</t>
+  </si>
+  <si>
+    <t>Dr. Bryan Michalowicz</t>
+  </si>
+  <si>
+    <t>(651) 429-2299</t>
+  </si>
+  <si>
+    <t>Dental implants periodontist</t>
+  </si>
+  <si>
+    <t>2500 Como Ave, St Paul, MN 55108</t>
+  </si>
+  <si>
+    <t>43</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/Dr.+Bryan+Michalowicz/data=!4m7!3m6!1s0x52b32cf33695c23d:0xa13957eb0ef804e4!8m2!3d44.9865133!4d-93.2019148!16s%2Fg%2F11p07b1_46!19sChIJPcKVNvMss1IR5AT4DutXOaE?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>2026-10-25T09:03:47.733Z</t>
+  </si>
+  <si>
+    <t>Dr. David Rischall</t>
+  </si>
+  <si>
+    <t>(651) 690-5262</t>
+  </si>
+  <si>
+    <t>1845 Grand Ave, St Paul, MN 55105</t>
+  </si>
+  <si>
+    <t>3.6</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/Dr.+David+Rischall/data=!4m7!3m6!1s0x87f629f58f5540f1:0x60c8c138c859df04!8m2!3d44.9402935!4d-93.1782798!16s%2Fg%2F1xg5t71t!19sChIJ8UBVj_Up9ocRBN9ZyDjByGA?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>2026-10-25T09:03:51.595Z</t>
+  </si>
+  <si>
+    <t>The Dental Doctors</t>
+  </si>
+  <si>
+    <t>(507) 281-3926</t>
+  </si>
+  <si>
+    <t>723 2nd St SW, Rochester, MN 55902</t>
+  </si>
+  <si>
+    <t>Rochester</t>
+  </si>
+  <si>
+    <t>4.7</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/The+Dental+Doctors/data=!4m7!3m6!1s0x87f75f71d9a3ed83:0xa723e5ca84dd08bb!8m2!3d44.0218925!4d-92.473526!16s%2Fg%2F11cmp0gv85!19sChIJg-2j2XFf94cRuwjdhMrlI6c?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>2026-10-25T09:04:07.454Z</t>
+  </si>
+  <si>
+    <t>Downtown Dental Care: Deborrah J Nordblom, DDS</t>
+  </si>
+  <si>
+    <t>(507) 285-1121</t>
+  </si>
+  <si>
+    <t>212 1st Ave SW #30, Rochester, MN 55902</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/Downtown+Dental+Care:+Deborrah+J+Nordblom,+DDS/data=!4m7!3m6!1s0x87f75f6338b315a1:0x98f0cc85b4d3bc3!8m2!3d44.0210999!4d-92.464071!16s%2Fg%2F1v44fjlh!19sChIJoRWzOGNf94cRwztNW8gMjwk?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>2026-10-25T09:04:11.685Z</t>
+  </si>
+  <si>
+    <t>Clinical Mastery</t>
+  </si>
+  <si>
+    <t>(507) 273-9396</t>
+  </si>
+  <si>
+    <t>2032 Valleyhigh Dr NW, Rochester, MN 55901</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/Clinical+Mastery/data=!4m7!3m6!1s0x87f75f8ebb03ffeb:0x7ca107a3dd3d1e2a!8m2!3d44.0384899!4d-92.4953551!16s%2Fg%2F11ygl1qm3v!19sChIJ6_8Du45f94cRKh493aMHoXw?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>2026-10-25T09:04:13.917Z</t>
+  </si>
+  <si>
+    <t>Dr. Jacob M. Peters, DDS</t>
+  </si>
+  <si>
+    <t>(507) 288-1188</t>
+  </si>
+  <si>
+    <t>1011 Bel Air Ln NW, Rochester, MN 55901</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/Dr.+Jacob+M.+Peters,+DDS/data=!4m7!3m6!1s0x87f75fe793fb0979:0x424e79643d0ecee5!8m2!3d44.0611784!4d-92.4793012!16s%2Fg%2F1tt8cv2l!19sChIJeQn7k-df94cR5c4OPWR5TkI?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>2026-10-25T09:04:18.682Z</t>
+  </si>
+  <si>
+    <t>Dr. Phillip D. Vickers, DDS</t>
+  </si>
+  <si>
+    <t>(507) 281-5820</t>
+  </si>
+  <si>
+    <t>2717 Superior Dr NW # B, Rochester, MN 55901</t>
+  </si>
+  <si>
+    <t>3.4</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/Dr.+Phillip+D.+Vickers,+DDS/data=!4m7!3m6!1s0x87f75e1382e1ef97:0xaf8726fedcf71fb1!8m2!3d44.051718!4d-92.52527!16s%2Fg%2F1tg_b12x!19sChIJl-_hghNe94cRsR_33P4mh68?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>2026-10-25T09:04:21.243Z</t>
+  </si>
+  <si>
+    <t>Dr. Adam J. Kelly, DMD</t>
+  </si>
+  <si>
+    <t>(507) 280-7557</t>
+  </si>
+  <si>
+    <t>2475 Georgetowne Dr NW, Rochester, MN 55901</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/Dr.+Adam+J.+Kelly,+DMD/data=!4m7!3m6!1s0x87f76062bdf78051:0xe033d05a1a6a1ed5!8m2!3d44.079219!4d-92.4992689!16s%2Fg%2F1w0h81z_!19sChIJUYD3vWJg94cR1R5qGlrQM-A?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>2026-10-25T09:04:23.485Z</t>
+  </si>
+  <si>
+    <t>Dr. Sonya Josephs, DMD</t>
+  </si>
+  <si>
+    <t>(507) 287-8320</t>
+  </si>
+  <si>
+    <t>3000 43rd St NW, Rochester, MN 55901</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/Dr.+Sonya+Josephs,+DMD/data=!4m7!3m6!1s0x87f75e28385a918b:0x5876fd69e4c50e06!8m2!3d44.0674552!4d-92.5080873!16s%2Fg%2F1tfg3nbr!19sChIJi5FaOChe94cRBg7F5Gn9dlg?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>2026-10-25T09:06:26.340Z</t>
+  </si>
+  <si>
+    <t>Prosthetic Laboratories</t>
+  </si>
+  <si>
+    <t>(507) 281-5250</t>
+  </si>
+  <si>
+    <t>Orthotics &amp; prosthetics service</t>
+  </si>
+  <si>
+    <t>121 23rd Ave SW Ste 103, Rochester, MN 55902</t>
+  </si>
+  <si>
+    <t>2</t>
+  </si>
+  <si>
+    <t>SundayClosed; Monday8 AM–5 PM; Tuesday8 AM–5 PM; Wednesday8 AM–5 PM; Thursday8 AM–5 PM; Friday8 AM–5 PM; SaturdayClosed</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/Prosthetic+Laboratories/data=!4m7!3m6!1s0x87f75efd604bf5d7:0xa949402a816073b7!8m2!3d44.0225587!4d-92.5000966!16s%2Fg%2F1tf9yzx_!19sChIJ1_VLYP1e94cRt3NggSpASak?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>2026-10-25T09:06:41.046Z</t>
+  </si>
+  <si>
+    <t>Todays Urgent Dentist</t>
+  </si>
+  <si>
+    <t>(507) 353-8619</t>
+  </si>
+  <si>
+    <t>603 6th Ave NW, Rochester, MN 55901</t>
+  </si>
+  <si>
+    <t>3.0</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/Todays+Urgent+Dentist/data=!4m7!3m6!1s0x87f75f825461a67d:0x28bc76985d39a591!8m2!3d44.02973!4d-92.471291!16s%2Fg%2F11pdr80ddz!19sChIJfaZhVIJf94cRkaU5XZh2vCg?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>2026-10-25T09:07:06.008Z</t>
+  </si>
+  <si>
+    <t>Dr. Enrico DiVito Emergency Dental Service</t>
+  </si>
+  <si>
+    <t>(507) 306-0900</t>
+  </si>
+  <si>
+    <t>406 3rd Ave SE, Rochester, MN 55904</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/Dr.+Enrico+DiVito+Emergency+Dental+Service/data=!4m7!3m6!1s0x87f9e1e1ab40c02d:0xa52f3cfcf11e6ca1!8m2!3d44.018975!4d-92.458518!16s%2Fg%2F11nvf7n90l!19sChIJLcBAq-Hh-YcRoWwe8fw8L6U?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>2026-10-25T09:07:08.318Z</t>
+  </si>
+  <si>
+    <t>Jason Naud</t>
+  </si>
+  <si>
+    <t>(507) 284-2511</t>
+  </si>
+  <si>
+    <t>Dept Dental, 200 1st St SW, Rochester, MN 55905</t>
+  </si>
+  <si>
+    <t>50</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/Jason+Naud/data=!4m7!3m6!1s0x87f75f7b39000001:0x76fd356c23b6f948!8m2!3d44.0226729!4d-92.4667508!16s%2Fg%2F11sd2x_x4v!19sChIJAQAAOXtf94cRSPm2I2w1_XY?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>2026-10-25T09:07:53.074Z</t>
+  </si>
+  <si>
+    <t>Summit Dental Clinic</t>
+  </si>
+  <si>
+    <t>(218) 722-1846</t>
+  </si>
+  <si>
+    <t>2730 Piedmont Ave Ste 3, Duluth, MN 55811</t>
+  </si>
+  <si>
+    <t>Duluth</t>
+  </si>
+  <si>
+    <t>4.6</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/Summit+Dental+Clinic/data=!4m7!3m6!1s0x52ae4ce1e0ee15b1:0x3b1d9069cbe1b123!8m2!3d46.7823755!4d-92.1592364!16s%2Fg%2F1tdfmxtm!19sChIJsRXu4OFMrlIRI7Hhy2mQHTs?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>2026-10-25T09:08:06.937Z</t>
+  </si>
+  <si>
+    <t>Noble Dental</t>
+  </si>
+  <si>
+    <t>(218) 722-2575</t>
+  </si>
+  <si>
+    <t>412 N Central Ave, Duluth, MN 55807</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/Noble+Dental/data=!4m7!3m6!1s0x52ae4c307f92208b:0xe52f6e5f9e1f9343!8m2!3d46.7394157!4d-92.166235!16s%2Fg%2F1q6j93kg2!19sChIJiyCSfzBMrlIRQ5Mfnl9uL-U?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>2026-10-25T09:08:09.184Z</t>
+  </si>
+  <si>
+    <t>Dr. Seth Amadio</t>
+  </si>
+  <si>
+    <t>(218) 728-6445</t>
+  </si>
+  <si>
+    <t>1225 E 1st St, Duluth, MN 55805</t>
+  </si>
+  <si>
+    <t>4.0</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/Dr.+Seth+Amadio/data=!4m7!3m6!1s0x52ae52d113faaaab:0xe93ced29cee711bb!8m2!3d46.8000889!4d-92.0836598!16s%2Fg%2F11rwxg1zfx!19sChIJq6r6E9FSrlIRuxHnzintPOk?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>2026-10-25T09:08:11.341Z</t>
+  </si>
+  <si>
+    <t>Johnson Michael R DDS</t>
+  </si>
+  <si>
+    <t>(218) 722-1497</t>
+  </si>
+  <si>
+    <t>4325 Grand Ave, Duluth, MN 55807</t>
+  </si>
+  <si>
+    <t>2.5</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/Johnson+Michael+R+DDS/data=!4m7!3m6!1s0x52ae4db53769f793:0x558e9275f1c92361!8m2!3d46.7482666!4d-92.1566512!16s%2Fg%2F1tk8bry0!19sChIJk_dpN7VNrlIRYSPJ8XWSjlU?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>2026-10-25T09:08:15.678Z</t>
+  </si>
+  <si>
+    <t>Dr. Stephen D. Johnson, DDS</t>
+  </si>
+  <si>
+    <t>(218) 727-5041</t>
+  </si>
+  <si>
+    <t>324 W Superior St #930, Duluth, MN 55802</t>
+  </si>
+  <si>
+    <t>SundayOpen 24 hours</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/Dr.+Stephen+D.+Johnson,+DDS/data=!4m7!3m6!1s0x52ae52968fc52ff3:0x4dae9cc9b76d9df5!8m2!3d46.7832587!4d-92.1024519!16s%2Fg%2F1tfql0jv!19sChIJ8y_Fj5ZSrlIR9Z1tt8mcrk0?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>2026-10-25T09:08:18.169Z</t>
+  </si>
+  <si>
+    <t>Dr. Kyle Hammer</t>
+  </si>
+  <si>
+    <t>(218) 728-5095</t>
+  </si>
+  <si>
+    <t>1432 London Rd, Duluth, MN 55805</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/Dr.+Kyle+Hammer/data=!4m7!3m6!1s0x52ae52d636540001:0x510b5dc527d20ea5!8m2!3d46.7996486!4d-92.077888!16s%2Fg%2F11rwxg5xqz!19sChIJAQBUNtZSrlIRpQ7SJ8VdC1E?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>2026-10-25T09:08:20.656Z</t>
+  </si>
+  <si>
+    <t>Gatlin Jr Wayne C DDS</t>
+  </si>
+  <si>
+    <t>(218) 727-2772</t>
+  </si>
+  <si>
+    <t>324 W Superior St #404, Duluth, MN 55802</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/Gatlin+Jr+Wayne+C+DDS/data=!4m7!3m6!1s0x52ae52968fc52ff3:0x384cd04c12e8033!8m2!3d46.7832587!4d-92.1024519!16s%2Fg%2F1tp26y07!19sChIJ8y_Fj5ZSrlIRM4AuwQTNhAM?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>2026-10-25T09:08:23.194Z</t>
+  </si>
+  <si>
+    <t>Dr. Gregory H. Kaake, DDS.</t>
+  </si>
+  <si>
+    <t>(218) 722-1070</t>
+  </si>
+  <si>
+    <t>1832 Maple Grove Rd, Duluth, MN 55811</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/Dr.+Gregory+H.+Kaake,+DDS./data=!4m7!3m6!1s0x52afb32b9f388a89:0xd46a8de70c3419ac!8m2!3d46.8107169!4d-92.1658688!16s%2Fg%2F1tt1gw1p!19sChIJiYo4nyuzr1IRrBk0DOeNatQ?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>2026-10-25T09:08:36.565Z</t>
+  </si>
+  <si>
+    <t>Trygstad Paul M</t>
+  </si>
+  <si>
+    <t>(218) 628-1810</t>
+  </si>
+  <si>
+    <t>416 N Central Ave #1, Duluth, MN 55807</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/Trygstad+Paul+M/data=!4m7!3m6!1s0x52ae4c3a7e26c977:0x7868c04f501d5368!8m2!3d46.7395989!4d-92.166055!16s%2Fg%2F12620lf1v!19sChIJd8kmfjpMrlIRaFMdUE_AaHg?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>2026-10-25T09:08:40.472Z</t>
+  </si>
+  <si>
+    <t>Spoelhof Heidi DDS</t>
+  </si>
+  <si>
+    <t>(218) 722-0823</t>
+  </si>
+  <si>
+    <t>2860 Piedmont Ave, Duluth, MN 55811</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/Spoelhof+Heidi+DDS/data=!4m7!3m6!1s0x52ae4ce1ad09cb99:0x13a22ac64f73a62e!8m2!3d46.7838143!4d-92.1616563!16s%2Fg%2F1tfcmz_h!19sChIJmcsJreFMrlIRLqZzT8YqohM?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>2026-10-25T09:08:43.161Z</t>
+  </si>
+  <si>
+    <t>Homestead Family Dental</t>
+  </si>
+  <si>
+    <t>(218) 525-9020</t>
+  </si>
+  <si>
+    <t>5722 Homestead Rd # C, Duluth, MN 55804</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/Homestead+Family+Dental/data=!4m7!3m6!1s0x52af044d5579dfe3:0x2d480e7b9603b339!8m2!3d46.9266084!4d-91.8465256!16s%2Fg%2F1tsljc86!19sChIJ4995VU0Er1IRObMDlnsOSC0?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>2026-10-25T09:08:52.605Z</t>
+  </si>
+  <si>
+    <t>Family &amp; Cosmetic Dental Care.</t>
+  </si>
+  <si>
+    <t>(218) 722-1115</t>
+  </si>
+  <si>
+    <t>1001 E Central Entrance, Duluth, MN 55811</t>
+  </si>
+  <si>
+    <t>2.0</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/Family+%26+Cosmetic+Dental+Care./data=!4m7!3m6!1s0x52ae52afec23ea8b:0xc93c1f07d527d1aa!8m2!3d46.7995225!4d-92.1136546!16s%2Fg%2F1tdmv7zs!19sChIJi-oj7K9SrlIRqtEn1QcfPMk?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>2026-10-25T09:08:55.129Z</t>
+  </si>
+  <si>
+    <t>Zibell Dental Laboratories Inc</t>
+  </si>
+  <si>
+    <t>(218) 722-4754</t>
+  </si>
+  <si>
+    <t>Dental laboratory</t>
+  </si>
+  <si>
+    <t>324 W Superior St #522, Duluth, MN 55802</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/Zibell+Dental+Laboratories+Inc/data=!4m7!3m6!1s0x52ae52968fc52ff3:0x4dd443dac1fc6aff!8m2!3d46.7832587!4d-92.1024519!16s%2Fg%2F1tdcr4zt!19sChIJ8y_Fj5ZSrlIR_2r8wdpD1E0?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>2026-10-25T09:09:15.380Z</t>
+  </si>
+  <si>
+    <t>Northern Dental Arts</t>
+  </si>
+  <si>
+    <t>(218) 728-4488</t>
+  </si>
+  <si>
+    <t>925 E Superior St #101, Duluth, MN 55802</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/Northern+Dental+Arts/data=!4m7!3m6!1s0x52ae52daa6062851:0xb6243342ea223f27!8m2!3d46.7963932!4d-92.0864294!16s%2Fg%2F1td5frwq!19sChIJUSgGptpSrlIRJz8i6kIzJLY?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>2026-10-25T09:09:18.162Z</t>
+  </si>
+  <si>
+    <t>Dr. Susan Guirguis, DDS</t>
+  </si>
+  <si>
+    <t>(218) 525-5100</t>
+  </si>
+  <si>
+    <t>2710 Piedmont Ave Suite A, Duluth, MN 55811</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/Dr.+Susan+Guirguis,+DDS/data=!4m7!3m6!1s0x52ae4d1e1e508a4b:0x43c522369b1a5e83!8m2!3d46.7821387!4d-92.1589167!16s%2Fg%2F1td423wm!19sChIJS4pQHh5NrlIRg14amzYixUM?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>2026-10-25T09:09:20.459Z</t>
+  </si>
+  <si>
+    <t>Dr. Mark Bruzek</t>
+  </si>
+  <si>
+    <t>(218) 728-2117</t>
+  </si>
+  <si>
+    <t>4419 Air Base Rd, Hermantown, MN 55811</t>
+  </si>
+  <si>
+    <t>Hermantown</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/Dr.+Mark+Bruzek/data=!4m7!3m6!1s0x52afb36c09e64f6b:0xdd209347033fb753!8m2!3d46.8286929!4d-92.1877109!16s%2Fg%2F11k3xs49f8!19sChIJa0_mCWyzr1IRU7c_A0eTIN0?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>2026-10-25T09:09:29.261Z</t>
+  </si>
+  <si>
+    <t>Kundel Pediatric Associates Pa: Anderson Suzanne</t>
+  </si>
+  <si>
+    <t>(218) 722-1408</t>
+  </si>
+  <si>
+    <t>1000 E 1st St #204, Duluth, MN 55805</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/Kundel+Pediatric+Associates+Pa:+Anderson+Suzanne/data=!4m7!3m6!1s0x52ae526400000001:0x49d977e191305bfb!8m2!3d46.7974813!4d-92.0857789!16s%2Fg%2F1vzg1wys!19sChIJAQAAAGRSrlIR-1swkeF32Uk?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>2026-10-25T09:09:31.375Z</t>
+  </si>
+  <si>
+    <t>Dr. Kirstin Carlson</t>
+  </si>
+  <si>
+    <t>(218) 262-5488</t>
+  </si>
+  <si>
+    <t>Orthodontist</t>
+  </si>
+  <si>
+    <t>3617 W Arrowhead Rd, Duluth, MN 55811</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/Dr.+Kirstin+Carlson/data=!4m7!3m6!1s0x52afb2c1bbd00001:0x3a3555d069955894!8m2!3d46.8230877!4d-92.1446035!16s%2Fg%2F11rwxg38k_!19sChIJAQDQu8Gyr1IRlFiVadBVNTo?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>2026-10-25T09:09:46.707Z</t>
+  </si>
+  <si>
+    <t>Smiles on Point</t>
+  </si>
+  <si>
+    <t>(218) 395-8751</t>
+  </si>
+  <si>
+    <t>216 W Superior St, Duluth, MN 55802</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/Smiles+on+Point/data=!4m7!3m6!1s0x52ae535b474ef6bb:0x4cc1d66e332d8bb1!8m2!3d46.784398!4d-92.100982!16s%2Fg%2F11ww0t29xb!19sChIJu_ZOR1tTrlIRsYstM27WwUw?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>2026-10-25T09:10:06.934Z</t>
+  </si>
+  <si>
+    <t>DMR Dental Studio</t>
+  </si>
+  <si>
+    <t>(952) 888-0379</t>
+  </si>
+  <si>
+    <t>9301 Bryant Ave S, Bloomington, MN 55420</t>
+  </si>
+  <si>
+    <t>Bloomington</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/DMR+Dental+Studio/data=!4m7!3m6!1s0x87f62505dabb2e09:0xe87451d8f51a3b73!8m2!3d44.8354217!4d-93.2906592!16s%2Fg%2F12638qz2j!19sChIJCS672gUl9ocRczsa9dhRdOg?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>2026-10-25T09:11:00.293Z</t>
+  </si>
+  <si>
+    <t>Dr. Frank Russomanno Jr, DDS</t>
+  </si>
+  <si>
+    <t>(952) 881-0504</t>
+  </si>
+  <si>
+    <t>8910 Penn Ave S, Minneapolis, MN 55431</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/Dr.+Frank+Russomanno+Jr,+DDS/data=!4m7!3m6!1s0x87f62458309731a3:0x3ca229d5e3914b07!8m2!3d44.8420077!4d-93.3093464!16s%2Fg%2F1v_vtgd4!19sChIJozGXMFgk9ocRB0uR49Upojw?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>2026-10-25T09:11:18.086Z</t>
+  </si>
+  <si>
+    <t>Neil Keane, DDS</t>
+  </si>
+  <si>
+    <t>(952) 888-8181</t>
+  </si>
+  <si>
+    <t>8910 Penn Ave S, Bloomington, MN 55431</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/Neil+Keane,+DDS/data=!4m7!3m6!1s0x87f624581ed832bb:0xdcc0326a79d0df87!8m2!3d44.8419936!4d-93.3093783!16s%2Fg%2F12q4rmhm0!19sChIJuzLYHlgk9ocRh9_QeWoywNw?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>2026-10-25T09:11:20.043Z</t>
+  </si>
+  <si>
+    <t>Dr. Heidi J. Pound, DDS</t>
+  </si>
+  <si>
+    <t>(612) 543-2500</t>
+  </si>
+  <si>
+    <t>2105 W 80th 1/2 St, Bloomington, MN 55431</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/Dr.+Heidi+J.+Pound,+DDS/data=!4m7!3m6!1s0x52b333a961137bf3:0x2b35f7feac927176!8m2!3d44.8575573!4d-93.3065406!16s%2Fg%2F1tt1gw53!19sChIJ83sTYakzs1IRdnGSrP73NSs?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>2026-10-25T09:11:22.341Z</t>
+  </si>
+  <si>
+    <t>Hultstrand Glen DDS</t>
+  </si>
+  <si>
+    <t>(952) 746-8188</t>
+  </si>
+  <si>
+    <t>8120 Penn Ave S Ste 115, Minneapolis, MN 55431</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/Hultstrand+Glen+DDS/data=!4m7!3m6!1s0x87f6244628e0b861:0x8506a4027f4e538b!8m2!3d44.8560505!4d-93.310359!16s%2Fg%2F1vxzb5f1!19sChIJYbjgKEYk9ocRi1NOfwKkBoU?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>2026-10-25T09:11:24.890Z</t>
+  </si>
+  <si>
+    <t>Beverly Smile - Bloomington</t>
+  </si>
+  <si>
+    <t>(612) 460-5817</t>
+  </si>
+  <si>
+    <t>Teeth whitening service</t>
+  </si>
+  <si>
+    <t>7989 Southtown Dr, Bloomington, MN 55431</t>
+  </si>
+  <si>
+    <t>Sunday10 AM–5 PM</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/Beverly+Smile+-+Bloomington/data=!4m7!3m6!1s0x87f625b3f6a9c28f:0x7d7585fbb22da535!8m2!3d44.8593123!4d-93.3068294!16s%2Fg%2F11p09qlvld!19sChIJj8Kp9rMl9ocRNaUtsvuFdX0?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>2026-10-25T09:12:50.229Z</t>
+  </si>
+  <si>
+    <t>Affliated Pediatric Dentists</t>
+  </si>
+  <si>
+    <t>(952) 435-4102</t>
+  </si>
+  <si>
+    <t>14050 Nicollet Ave #100, Burnsville, MN 55337</t>
+  </si>
+  <si>
+    <t>Burnsville</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/Affliated+Pediatric+Dentists/data=!4m7!3m6!1s0x87f63a401e0d48f3:0x78b57037fb15cb08!8m2!3d44.7483869!4d-93.2788529!16s%2Fg%2F1260fz8vg!19sChIJ80gNHkA69ocRCMsV-zdwtXg?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>2026-10-25T09:13:45.005Z</t>
+  </si>
+  <si>
+    <t>Lindsay Bedeaux</t>
+  </si>
+  <si>
+    <t>(952) 428-0200</t>
+  </si>
+  <si>
+    <t>7373 France Ave S Ste 400, Edina, MN 55435</t>
+  </si>
+  <si>
+    <t>Edina</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/Lindsay+Bedeaux/data=!4m7!3m6!1s0x87f6241aea155555:0x9f15c4e6bc3971cb!8m2!3d44.8690425!4d-93.3274806!16s%2Fg%2F11sd2x_bb7!19sChIJVVUV6hok9ocRy3E5vObEFZ8?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>2026-10-25T09:13:46.983Z</t>
+  </si>
+  <si>
+    <t>Dr. Kurt J. King, DDS</t>
+  </si>
+  <si>
+    <t>(952) 831-4400</t>
+  </si>
+  <si>
+    <t>7373 France Ave S #402, Minneapolis, MN 55435</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/Dr.+Kurt+J.+King,+DDS/data=!4m7!3m6!1s0x87f6241ac04767bd:0x28da66f38c780007!8m2!3d44.8690153!4d-93.327475!16s%2Fg%2F1tdb07hy!19sChIJvWdHwBok9ocRBwB4jPNm2ig?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>2026-10-25T09:13:48.878Z</t>
+  </si>
+  <si>
+    <t>Dr. George A. Hankerson, DDS</t>
+  </si>
+  <si>
+    <t>(952) 440-5100</t>
+  </si>
+  <si>
+    <t>7629 Egan Dr, Savage, MN 55378</t>
+  </si>
+  <si>
+    <t>Savage</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/Dr.+George+A.+Hankerson,+DDS/data=!4m7!3m6!1s0x87f63c4abd14816f:0xf42e2de619167ff4!8m2!3d44.7453325!4d-93.3781593!16s%2Fg%2F1tj85dhv!19sChIJb4EUvUo89ocR9H8WGeYtLvQ?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>2026-10-25T09:13:52.585Z</t>
+  </si>
+  <si>
+    <t>John Gawlik</t>
+  </si>
+  <si>
+    <t>(952) 884-8337</t>
+  </si>
+  <si>
+    <t>8100 Penn Ave S Ste 172, Bloomington, MN 554311325</t>
+  </si>
+  <si>
+    <t>1.0</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/John+Gawlik/data=!4m7!3m6!1s0x87f624462e1573e9:0x35cdb4e4ea6debb8!8m2!3d44.8561436!4d-93.3092367!16s%2Fg%2F11rkj9gmm_!19sChIJ6XMVLkYk9ocRuOtt6uS0zTU?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>2026-10-25T09:15:02.097Z</t>
+  </si>
+  <si>
+    <t>Dr. Gregory B. Hanson, DDS</t>
+  </si>
+  <si>
+    <t>(952) 835-0666</t>
+  </si>
+  <si>
+    <t>5270 W 84th St, Bloomington, MN 55437</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/Dr.+Gregory+B.+Hanson,+DDS/data=!4m7!3m6!1s0x87f6238e16e6117f:0xb4082fb8f3e94311!8m2!3d44.8523322!4d-93.3482686!16s%2Fg%2F1td7j91p!19sChIJfxHmFo4j9ocREUPp87gvCLQ?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>2026-10-25T09:15:18.495Z</t>
+  </si>
+  <si>
+    <t>Dr. Erik Unger</t>
+  </si>
+  <si>
+    <t>(651) 236-7458</t>
+  </si>
+  <si>
+    <t>3405 Promenade Ave Unit 300, Eagan, MN 55123</t>
+  </si>
+  <si>
+    <t>Eagan</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/Dr.+Erik+Unger/data=!4m7!3m6!1s0x87f62db99e4fffff:0xc18b4dfef507bccf!8m2!3d44.8329559!4d-93.1539277!16s%2Fg%2F11qgb6m6rl!19sChIJ__9Pnrkt9ocRz7wH9f5Ni8E?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>2026-10-25T09:15:20.871Z</t>
   </si>
 </sst>
 </file>
@@ -649,7 +1597,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:M12"/>
+  <dimension ref="A1:M67"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="34" customWidth="1"/>
@@ -1158,6 +2106,2261 @@
         <v>85</v>
       </c>
     </row>
+    <row r="13" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A13" t="s">
+        <v>86</v>
+      </c>
+      <c r="B13" t="s">
+        <v>87</v>
+      </c>
+      <c r="C13" t="s">
+        <v>15</v>
+      </c>
+      <c r="D13" t="s">
+        <v>88</v>
+      </c>
+      <c r="E13" t="s">
+        <v>89</v>
+      </c>
+      <c r="F13" t="s">
+        <v>18</v>
+      </c>
+      <c r="G13" t="s">
+        <v>19</v>
+      </c>
+      <c r="H13" t="s">
+        <v>20</v>
+      </c>
+      <c r="I13" t="s">
+        <v>21</v>
+      </c>
+      <c r="J13" t="s">
+        <v>90</v>
+      </c>
+      <c r="K13" t="s">
+        <v>23</v>
+      </c>
+      <c r="L13" t="s">
+        <v>91</v>
+      </c>
+      <c r="M13" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="14" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A14" t="s">
+        <v>93</v>
+      </c>
+      <c r="B14" t="s">
+        <v>94</v>
+      </c>
+      <c r="C14" t="s">
+        <v>95</v>
+      </c>
+      <c r="D14" t="s">
+        <v>96</v>
+      </c>
+      <c r="E14" t="s">
+        <v>17</v>
+      </c>
+      <c r="F14" t="s">
+        <v>18</v>
+      </c>
+      <c r="G14" t="s">
+        <v>19</v>
+      </c>
+      <c r="H14" t="s">
+        <v>97</v>
+      </c>
+      <c r="I14" t="s">
+        <v>36</v>
+      </c>
+      <c r="J14" t="s">
+        <v>20</v>
+      </c>
+      <c r="K14" t="s">
+        <v>23</v>
+      </c>
+      <c r="L14" t="s">
+        <v>98</v>
+      </c>
+      <c r="M14" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="15" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A15" t="s">
+        <v>100</v>
+      </c>
+      <c r="B15" t="s">
+        <v>101</v>
+      </c>
+      <c r="C15" t="s">
+        <v>28</v>
+      </c>
+      <c r="D15" t="s">
+        <v>102</v>
+      </c>
+      <c r="E15" t="s">
+        <v>103</v>
+      </c>
+      <c r="F15" t="s">
+        <v>18</v>
+      </c>
+      <c r="G15" t="s">
+        <v>19</v>
+      </c>
+      <c r="H15" t="s">
+        <v>104</v>
+      </c>
+      <c r="I15" t="s">
+        <v>36</v>
+      </c>
+      <c r="J15" t="s">
+        <v>105</v>
+      </c>
+      <c r="K15" t="s">
+        <v>23</v>
+      </c>
+      <c r="L15" t="s">
+        <v>106</v>
+      </c>
+      <c r="M15" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="16" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A16" t="s">
+        <v>108</v>
+      </c>
+      <c r="B16" t="s">
+        <v>109</v>
+      </c>
+      <c r="C16" t="s">
+        <v>15</v>
+      </c>
+      <c r="D16" t="s">
+        <v>110</v>
+      </c>
+      <c r="E16" t="s">
+        <v>111</v>
+      </c>
+      <c r="F16" t="s">
+        <v>18</v>
+      </c>
+      <c r="G16" t="s">
+        <v>19</v>
+      </c>
+      <c r="H16" t="s">
+        <v>20</v>
+      </c>
+      <c r="I16" t="s">
+        <v>21</v>
+      </c>
+      <c r="J16" t="s">
+        <v>20</v>
+      </c>
+      <c r="K16" t="s">
+        <v>23</v>
+      </c>
+      <c r="L16" t="s">
+        <v>112</v>
+      </c>
+      <c r="M16" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="17" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A17" t="s">
+        <v>114</v>
+      </c>
+      <c r="B17" t="s">
+        <v>115</v>
+      </c>
+      <c r="C17" t="s">
+        <v>15</v>
+      </c>
+      <c r="D17" t="s">
+        <v>116</v>
+      </c>
+      <c r="E17" t="s">
+        <v>103</v>
+      </c>
+      <c r="F17" t="s">
+        <v>18</v>
+      </c>
+      <c r="G17" t="s">
+        <v>19</v>
+      </c>
+      <c r="H17" t="s">
+        <v>20</v>
+      </c>
+      <c r="I17" t="s">
+        <v>21</v>
+      </c>
+      <c r="J17" t="s">
+        <v>20</v>
+      </c>
+      <c r="K17" t="s">
+        <v>23</v>
+      </c>
+      <c r="L17" t="s">
+        <v>117</v>
+      </c>
+      <c r="M17" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="18" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A18" t="s">
+        <v>119</v>
+      </c>
+      <c r="B18" t="s">
+        <v>120</v>
+      </c>
+      <c r="C18" t="s">
+        <v>121</v>
+      </c>
+      <c r="D18" t="s">
+        <v>122</v>
+      </c>
+      <c r="E18" t="s">
+        <v>103</v>
+      </c>
+      <c r="F18" t="s">
+        <v>18</v>
+      </c>
+      <c r="G18" t="s">
+        <v>19</v>
+      </c>
+      <c r="H18" t="s">
+        <v>35</v>
+      </c>
+      <c r="I18" t="s">
+        <v>36</v>
+      </c>
+      <c r="J18" t="s">
+        <v>20</v>
+      </c>
+      <c r="K18" t="s">
+        <v>23</v>
+      </c>
+      <c r="L18" t="s">
+        <v>123</v>
+      </c>
+      <c r="M18" t="s">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="19" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A19" t="s">
+        <v>125</v>
+      </c>
+      <c r="B19" t="s">
+        <v>126</v>
+      </c>
+      <c r="C19" t="s">
+        <v>127</v>
+      </c>
+      <c r="D19" t="s">
+        <v>128</v>
+      </c>
+      <c r="E19" t="s">
+        <v>103</v>
+      </c>
+      <c r="F19" t="s">
+        <v>18</v>
+      </c>
+      <c r="G19" t="s">
+        <v>19</v>
+      </c>
+      <c r="H19" t="s">
+        <v>35</v>
+      </c>
+      <c r="I19" t="s">
+        <v>36</v>
+      </c>
+      <c r="J19" t="s">
+        <v>20</v>
+      </c>
+      <c r="K19" t="s">
+        <v>23</v>
+      </c>
+      <c r="L19" t="s">
+        <v>129</v>
+      </c>
+      <c r="M19" t="s">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="20" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A20" t="s">
+        <v>131</v>
+      </c>
+      <c r="B20" t="s">
+        <v>132</v>
+      </c>
+      <c r="C20" t="s">
+        <v>127</v>
+      </c>
+      <c r="D20" t="s">
+        <v>133</v>
+      </c>
+      <c r="E20" t="s">
+        <v>103</v>
+      </c>
+      <c r="F20" t="s">
+        <v>18</v>
+      </c>
+      <c r="G20" t="s">
+        <v>19</v>
+      </c>
+      <c r="H20" t="s">
+        <v>134</v>
+      </c>
+      <c r="I20" t="s">
+        <v>36</v>
+      </c>
+      <c r="J20" t="s">
+        <v>20</v>
+      </c>
+      <c r="K20" t="s">
+        <v>23</v>
+      </c>
+      <c r="L20" t="s">
+        <v>135</v>
+      </c>
+      <c r="M20" t="s">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="21" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A21" t="s">
+        <v>137</v>
+      </c>
+      <c r="B21" t="s">
+        <v>138</v>
+      </c>
+      <c r="C21" t="s">
+        <v>127</v>
+      </c>
+      <c r="D21" t="s">
+        <v>139</v>
+      </c>
+      <c r="E21" t="s">
+        <v>140</v>
+      </c>
+      <c r="F21" t="s">
+        <v>18</v>
+      </c>
+      <c r="G21" t="s">
+        <v>19</v>
+      </c>
+      <c r="H21" t="s">
+        <v>35</v>
+      </c>
+      <c r="I21" t="s">
+        <v>36</v>
+      </c>
+      <c r="J21" t="s">
+        <v>20</v>
+      </c>
+      <c r="K21" t="s">
+        <v>23</v>
+      </c>
+      <c r="L21" t="s">
+        <v>141</v>
+      </c>
+      <c r="M21" t="s">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="22" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A22" t="s">
+        <v>143</v>
+      </c>
+      <c r="B22" t="s">
+        <v>144</v>
+      </c>
+      <c r="C22" t="s">
+        <v>15</v>
+      </c>
+      <c r="D22" t="s">
+        <v>145</v>
+      </c>
+      <c r="E22" t="s">
+        <v>103</v>
+      </c>
+      <c r="F22" t="s">
+        <v>18</v>
+      </c>
+      <c r="G22" t="s">
+        <v>19</v>
+      </c>
+      <c r="H22" t="s">
+        <v>146</v>
+      </c>
+      <c r="I22" t="s">
+        <v>36</v>
+      </c>
+      <c r="J22" t="s">
+        <v>90</v>
+      </c>
+      <c r="K22" t="s">
+        <v>23</v>
+      </c>
+      <c r="L22" t="s">
+        <v>147</v>
+      </c>
+      <c r="M22" t="s">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="23" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A23" t="s">
+        <v>149</v>
+      </c>
+      <c r="B23" t="s">
+        <v>150</v>
+      </c>
+      <c r="C23" t="s">
+        <v>151</v>
+      </c>
+      <c r="D23" t="s">
+        <v>152</v>
+      </c>
+      <c r="E23" t="s">
+        <v>103</v>
+      </c>
+      <c r="F23" t="s">
+        <v>18</v>
+      </c>
+      <c r="G23" t="s">
+        <v>19</v>
+      </c>
+      <c r="H23" t="s">
+        <v>20</v>
+      </c>
+      <c r="I23" t="s">
+        <v>153</v>
+      </c>
+      <c r="J23" t="s">
+        <v>20</v>
+      </c>
+      <c r="K23" t="s">
+        <v>23</v>
+      </c>
+      <c r="L23" t="s">
+        <v>154</v>
+      </c>
+      <c r="M23" t="s">
+        <v>155</v>
+      </c>
+    </row>
+    <row r="24" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A24" t="s">
+        <v>156</v>
+      </c>
+      <c r="B24" t="s">
+        <v>157</v>
+      </c>
+      <c r="C24" t="s">
+        <v>15</v>
+      </c>
+      <c r="D24" t="s">
+        <v>158</v>
+      </c>
+      <c r="E24" t="s">
+        <v>103</v>
+      </c>
+      <c r="F24" t="s">
+        <v>18</v>
+      </c>
+      <c r="G24" t="s">
+        <v>19</v>
+      </c>
+      <c r="H24" t="s">
+        <v>159</v>
+      </c>
+      <c r="I24" t="s">
+        <v>36</v>
+      </c>
+      <c r="J24" t="s">
+        <v>90</v>
+      </c>
+      <c r="K24" t="s">
+        <v>23</v>
+      </c>
+      <c r="L24" t="s">
+        <v>160</v>
+      </c>
+      <c r="M24" t="s">
+        <v>161</v>
+      </c>
+    </row>
+    <row r="25" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A25" t="s">
+        <v>162</v>
+      </c>
+      <c r="B25" t="s">
+        <v>163</v>
+      </c>
+      <c r="C25" t="s">
+        <v>15</v>
+      </c>
+      <c r="D25" t="s">
+        <v>164</v>
+      </c>
+      <c r="E25" t="s">
+        <v>165</v>
+      </c>
+      <c r="F25" t="s">
+        <v>18</v>
+      </c>
+      <c r="G25" t="s">
+        <v>19</v>
+      </c>
+      <c r="H25" t="s">
+        <v>166</v>
+      </c>
+      <c r="I25" t="s">
+        <v>36</v>
+      </c>
+      <c r="J25" t="s">
+        <v>90</v>
+      </c>
+      <c r="K25" t="s">
+        <v>23</v>
+      </c>
+      <c r="L25" t="s">
+        <v>167</v>
+      </c>
+      <c r="M25" t="s">
+        <v>168</v>
+      </c>
+    </row>
+    <row r="26" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A26" t="s">
+        <v>169</v>
+      </c>
+      <c r="B26" t="s">
+        <v>170</v>
+      </c>
+      <c r="C26" t="s">
+        <v>15</v>
+      </c>
+      <c r="D26" t="s">
+        <v>171</v>
+      </c>
+      <c r="E26" t="s">
+        <v>165</v>
+      </c>
+      <c r="F26" t="s">
+        <v>18</v>
+      </c>
+      <c r="G26" t="s">
+        <v>19</v>
+      </c>
+      <c r="H26" t="s">
+        <v>20</v>
+      </c>
+      <c r="I26" t="s">
+        <v>21</v>
+      </c>
+      <c r="J26" t="s">
+        <v>20</v>
+      </c>
+      <c r="K26" t="s">
+        <v>23</v>
+      </c>
+      <c r="L26" t="s">
+        <v>172</v>
+      </c>
+      <c r="M26" t="s">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="27" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A27" t="s">
+        <v>174</v>
+      </c>
+      <c r="B27" t="s">
+        <v>175</v>
+      </c>
+      <c r="C27" t="s">
+        <v>28</v>
+      </c>
+      <c r="D27" t="s">
+        <v>176</v>
+      </c>
+      <c r="E27" t="s">
+        <v>165</v>
+      </c>
+      <c r="F27" t="s">
+        <v>18</v>
+      </c>
+      <c r="G27" t="s">
+        <v>19</v>
+      </c>
+      <c r="H27" t="s">
+        <v>20</v>
+      </c>
+      <c r="I27" t="s">
+        <v>21</v>
+      </c>
+      <c r="J27" t="s">
+        <v>20</v>
+      </c>
+      <c r="K27" t="s">
+        <v>23</v>
+      </c>
+      <c r="L27" t="s">
+        <v>177</v>
+      </c>
+      <c r="M27" t="s">
+        <v>178</v>
+      </c>
+    </row>
+    <row r="28" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A28" t="s">
+        <v>179</v>
+      </c>
+      <c r="B28" t="s">
+        <v>180</v>
+      </c>
+      <c r="C28" t="s">
+        <v>15</v>
+      </c>
+      <c r="D28" t="s">
+        <v>181</v>
+      </c>
+      <c r="E28" t="s">
+        <v>165</v>
+      </c>
+      <c r="F28" t="s">
+        <v>18</v>
+      </c>
+      <c r="G28" t="s">
+        <v>19</v>
+      </c>
+      <c r="H28" t="s">
+        <v>20</v>
+      </c>
+      <c r="I28" t="s">
+        <v>21</v>
+      </c>
+      <c r="J28" t="s">
+        <v>90</v>
+      </c>
+      <c r="K28" t="s">
+        <v>23</v>
+      </c>
+      <c r="L28" t="s">
+        <v>182</v>
+      </c>
+      <c r="M28" t="s">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="29" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A29" t="s">
+        <v>184</v>
+      </c>
+      <c r="B29" t="s">
+        <v>185</v>
+      </c>
+      <c r="C29" t="s">
+        <v>71</v>
+      </c>
+      <c r="D29" t="s">
+        <v>186</v>
+      </c>
+      <c r="E29" t="s">
+        <v>165</v>
+      </c>
+      <c r="F29" t="s">
+        <v>18</v>
+      </c>
+      <c r="G29" t="s">
+        <v>19</v>
+      </c>
+      <c r="H29" t="s">
+        <v>187</v>
+      </c>
+      <c r="I29" t="s">
+        <v>36</v>
+      </c>
+      <c r="J29" t="s">
+        <v>20</v>
+      </c>
+      <c r="K29" t="s">
+        <v>23</v>
+      </c>
+      <c r="L29" t="s">
+        <v>188</v>
+      </c>
+      <c r="M29" t="s">
+        <v>189</v>
+      </c>
+    </row>
+    <row r="30" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A30" t="s">
+        <v>190</v>
+      </c>
+      <c r="B30" t="s">
+        <v>191</v>
+      </c>
+      <c r="C30" t="s">
+        <v>15</v>
+      </c>
+      <c r="D30" t="s">
+        <v>192</v>
+      </c>
+      <c r="E30" t="s">
+        <v>165</v>
+      </c>
+      <c r="F30" t="s">
+        <v>18</v>
+      </c>
+      <c r="G30" t="s">
+        <v>19</v>
+      </c>
+      <c r="H30" t="s">
+        <v>20</v>
+      </c>
+      <c r="I30" t="s">
+        <v>21</v>
+      </c>
+      <c r="J30" t="s">
+        <v>20</v>
+      </c>
+      <c r="K30" t="s">
+        <v>23</v>
+      </c>
+      <c r="L30" t="s">
+        <v>193</v>
+      </c>
+      <c r="M30" t="s">
+        <v>194</v>
+      </c>
+    </row>
+    <row r="31" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A31" t="s">
+        <v>195</v>
+      </c>
+      <c r="B31" t="s">
+        <v>196</v>
+      </c>
+      <c r="C31" t="s">
+        <v>46</v>
+      </c>
+      <c r="D31" t="s">
+        <v>197</v>
+      </c>
+      <c r="E31" t="s">
+        <v>165</v>
+      </c>
+      <c r="F31" t="s">
+        <v>18</v>
+      </c>
+      <c r="G31" t="s">
+        <v>19</v>
+      </c>
+      <c r="H31" t="s">
+        <v>35</v>
+      </c>
+      <c r="I31" t="s">
+        <v>36</v>
+      </c>
+      <c r="J31" t="s">
+        <v>90</v>
+      </c>
+      <c r="K31" t="s">
+        <v>23</v>
+      </c>
+      <c r="L31" t="s">
+        <v>198</v>
+      </c>
+      <c r="M31" t="s">
+        <v>199</v>
+      </c>
+    </row>
+    <row r="32" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A32" t="s">
+        <v>200</v>
+      </c>
+      <c r="B32" t="s">
+        <v>201</v>
+      </c>
+      <c r="C32" t="s">
+        <v>202</v>
+      </c>
+      <c r="D32" t="s">
+        <v>203</v>
+      </c>
+      <c r="E32" t="s">
+        <v>165</v>
+      </c>
+      <c r="F32" t="s">
+        <v>18</v>
+      </c>
+      <c r="G32" t="s">
+        <v>19</v>
+      </c>
+      <c r="H32" t="s">
+        <v>35</v>
+      </c>
+      <c r="I32" t="s">
+        <v>204</v>
+      </c>
+      <c r="J32" t="s">
+        <v>205</v>
+      </c>
+      <c r="K32" t="s">
+        <v>23</v>
+      </c>
+      <c r="L32" t="s">
+        <v>206</v>
+      </c>
+      <c r="M32" t="s">
+        <v>207</v>
+      </c>
+    </row>
+    <row r="33" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A33" t="s">
+        <v>208</v>
+      </c>
+      <c r="B33" t="s">
+        <v>209</v>
+      </c>
+      <c r="C33" t="s">
+        <v>127</v>
+      </c>
+      <c r="D33" t="s">
+        <v>210</v>
+      </c>
+      <c r="E33" t="s">
+        <v>165</v>
+      </c>
+      <c r="F33" t="s">
+        <v>18</v>
+      </c>
+      <c r="G33" t="s">
+        <v>19</v>
+      </c>
+      <c r="H33" t="s">
+        <v>211</v>
+      </c>
+      <c r="I33" t="s">
+        <v>36</v>
+      </c>
+      <c r="J33" t="s">
+        <v>20</v>
+      </c>
+      <c r="K33" t="s">
+        <v>23</v>
+      </c>
+      <c r="L33" t="s">
+        <v>212</v>
+      </c>
+      <c r="M33" t="s">
+        <v>213</v>
+      </c>
+    </row>
+    <row r="34" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A34" t="s">
+        <v>214</v>
+      </c>
+      <c r="B34" t="s">
+        <v>215</v>
+      </c>
+      <c r="C34" t="s">
+        <v>127</v>
+      </c>
+      <c r="D34" t="s">
+        <v>216</v>
+      </c>
+      <c r="E34" t="s">
+        <v>165</v>
+      </c>
+      <c r="F34" t="s">
+        <v>18</v>
+      </c>
+      <c r="G34" t="s">
+        <v>19</v>
+      </c>
+      <c r="H34" t="s">
+        <v>20</v>
+      </c>
+      <c r="I34" t="s">
+        <v>21</v>
+      </c>
+      <c r="J34" t="s">
+        <v>20</v>
+      </c>
+      <c r="K34" t="s">
+        <v>23</v>
+      </c>
+      <c r="L34" t="s">
+        <v>217</v>
+      </c>
+      <c r="M34" t="s">
+        <v>218</v>
+      </c>
+    </row>
+    <row r="35" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A35" t="s">
+        <v>219</v>
+      </c>
+      <c r="B35" t="s">
+        <v>220</v>
+      </c>
+      <c r="C35" t="s">
+        <v>151</v>
+      </c>
+      <c r="D35" t="s">
+        <v>221</v>
+      </c>
+      <c r="E35" t="s">
+        <v>165</v>
+      </c>
+      <c r="F35" t="s">
+        <v>18</v>
+      </c>
+      <c r="G35" t="s">
+        <v>19</v>
+      </c>
+      <c r="H35" t="s">
+        <v>20</v>
+      </c>
+      <c r="I35" t="s">
+        <v>222</v>
+      </c>
+      <c r="J35" t="s">
+        <v>20</v>
+      </c>
+      <c r="K35" t="s">
+        <v>23</v>
+      </c>
+      <c r="L35" t="s">
+        <v>223</v>
+      </c>
+      <c r="M35" t="s">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="36" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A36" t="s">
+        <v>225</v>
+      </c>
+      <c r="B36" t="s">
+        <v>226</v>
+      </c>
+      <c r="C36" t="s">
+        <v>15</v>
+      </c>
+      <c r="D36" t="s">
+        <v>227</v>
+      </c>
+      <c r="E36" t="s">
+        <v>228</v>
+      </c>
+      <c r="F36" t="s">
+        <v>18</v>
+      </c>
+      <c r="G36" t="s">
+        <v>19</v>
+      </c>
+      <c r="H36" t="s">
+        <v>229</v>
+      </c>
+      <c r="I36" t="s">
+        <v>36</v>
+      </c>
+      <c r="J36" t="s">
+        <v>20</v>
+      </c>
+      <c r="K36" t="s">
+        <v>23</v>
+      </c>
+      <c r="L36" t="s">
+        <v>230</v>
+      </c>
+      <c r="M36" t="s">
+        <v>231</v>
+      </c>
+    </row>
+    <row r="37" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A37" t="s">
+        <v>232</v>
+      </c>
+      <c r="B37" t="s">
+        <v>233</v>
+      </c>
+      <c r="C37" t="s">
+        <v>15</v>
+      </c>
+      <c r="D37" t="s">
+        <v>234</v>
+      </c>
+      <c r="E37" t="s">
+        <v>228</v>
+      </c>
+      <c r="F37" t="s">
+        <v>18</v>
+      </c>
+      <c r="G37" t="s">
+        <v>19</v>
+      </c>
+      <c r="H37" t="s">
+        <v>134</v>
+      </c>
+      <c r="I37" t="s">
+        <v>36</v>
+      </c>
+      <c r="J37" t="s">
+        <v>90</v>
+      </c>
+      <c r="K37" t="s">
+        <v>23</v>
+      </c>
+      <c r="L37" t="s">
+        <v>235</v>
+      </c>
+      <c r="M37" t="s">
+        <v>236</v>
+      </c>
+    </row>
+    <row r="38" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A38" t="s">
+        <v>237</v>
+      </c>
+      <c r="B38" t="s">
+        <v>238</v>
+      </c>
+      <c r="C38" t="s">
+        <v>15</v>
+      </c>
+      <c r="D38" t="s">
+        <v>239</v>
+      </c>
+      <c r="E38" t="s">
+        <v>228</v>
+      </c>
+      <c r="F38" t="s">
+        <v>18</v>
+      </c>
+      <c r="G38" t="s">
+        <v>19</v>
+      </c>
+      <c r="H38" t="s">
+        <v>240</v>
+      </c>
+      <c r="I38" t="s">
+        <v>36</v>
+      </c>
+      <c r="J38" t="s">
+        <v>20</v>
+      </c>
+      <c r="K38" t="s">
+        <v>23</v>
+      </c>
+      <c r="L38" t="s">
+        <v>241</v>
+      </c>
+      <c r="M38" t="s">
+        <v>242</v>
+      </c>
+    </row>
+    <row r="39" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A39" t="s">
+        <v>243</v>
+      </c>
+      <c r="B39" t="s">
+        <v>244</v>
+      </c>
+      <c r="C39" t="s">
+        <v>15</v>
+      </c>
+      <c r="D39" t="s">
+        <v>245</v>
+      </c>
+      <c r="E39" t="s">
+        <v>228</v>
+      </c>
+      <c r="F39" t="s">
+        <v>18</v>
+      </c>
+      <c r="G39" t="s">
+        <v>19</v>
+      </c>
+      <c r="H39" t="s">
+        <v>246</v>
+      </c>
+      <c r="I39" t="s">
+        <v>36</v>
+      </c>
+      <c r="J39" t="s">
+        <v>20</v>
+      </c>
+      <c r="K39" t="s">
+        <v>23</v>
+      </c>
+      <c r="L39" t="s">
+        <v>247</v>
+      </c>
+      <c r="M39" t="s">
+        <v>248</v>
+      </c>
+    </row>
+    <row r="40" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A40" t="s">
+        <v>249</v>
+      </c>
+      <c r="B40" t="s">
+        <v>250</v>
+      </c>
+      <c r="C40" t="s">
+        <v>15</v>
+      </c>
+      <c r="D40" t="s">
+        <v>251</v>
+      </c>
+      <c r="E40" t="s">
+        <v>228</v>
+      </c>
+      <c r="F40" t="s">
+        <v>18</v>
+      </c>
+      <c r="G40" t="s">
+        <v>19</v>
+      </c>
+      <c r="H40" t="s">
+        <v>35</v>
+      </c>
+      <c r="I40" t="s">
+        <v>36</v>
+      </c>
+      <c r="J40" t="s">
+        <v>252</v>
+      </c>
+      <c r="K40" t="s">
+        <v>23</v>
+      </c>
+      <c r="L40" t="s">
+        <v>253</v>
+      </c>
+      <c r="M40" t="s">
+        <v>254</v>
+      </c>
+    </row>
+    <row r="41" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A41" t="s">
+        <v>255</v>
+      </c>
+      <c r="B41" t="s">
+        <v>256</v>
+      </c>
+      <c r="C41" t="s">
+        <v>28</v>
+      </c>
+      <c r="D41" t="s">
+        <v>257</v>
+      </c>
+      <c r="E41" t="s">
+        <v>228</v>
+      </c>
+      <c r="F41" t="s">
+        <v>18</v>
+      </c>
+      <c r="G41" t="s">
+        <v>19</v>
+      </c>
+      <c r="H41" t="s">
+        <v>35</v>
+      </c>
+      <c r="I41" t="s">
+        <v>36</v>
+      </c>
+      <c r="J41" t="s">
+        <v>20</v>
+      </c>
+      <c r="K41" t="s">
+        <v>23</v>
+      </c>
+      <c r="L41" t="s">
+        <v>258</v>
+      </c>
+      <c r="M41" t="s">
+        <v>259</v>
+      </c>
+    </row>
+    <row r="42" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A42" t="s">
+        <v>260</v>
+      </c>
+      <c r="B42" t="s">
+        <v>261</v>
+      </c>
+      <c r="C42" t="s">
+        <v>15</v>
+      </c>
+      <c r="D42" t="s">
+        <v>262</v>
+      </c>
+      <c r="E42" t="s">
+        <v>228</v>
+      </c>
+      <c r="F42" t="s">
+        <v>18</v>
+      </c>
+      <c r="G42" t="s">
+        <v>19</v>
+      </c>
+      <c r="H42" t="s">
+        <v>35</v>
+      </c>
+      <c r="I42" t="s">
+        <v>36</v>
+      </c>
+      <c r="J42" t="s">
+        <v>20</v>
+      </c>
+      <c r="K42" t="s">
+        <v>23</v>
+      </c>
+      <c r="L42" t="s">
+        <v>263</v>
+      </c>
+      <c r="M42" t="s">
+        <v>264</v>
+      </c>
+    </row>
+    <row r="43" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A43" t="s">
+        <v>265</v>
+      </c>
+      <c r="B43" t="s">
+        <v>266</v>
+      </c>
+      <c r="C43" t="s">
+        <v>15</v>
+      </c>
+      <c r="D43" t="s">
+        <v>267</v>
+      </c>
+      <c r="E43" t="s">
+        <v>228</v>
+      </c>
+      <c r="F43" t="s">
+        <v>18</v>
+      </c>
+      <c r="G43" t="s">
+        <v>19</v>
+      </c>
+      <c r="H43" t="s">
+        <v>35</v>
+      </c>
+      <c r="I43" t="s">
+        <v>36</v>
+      </c>
+      <c r="J43" t="s">
+        <v>20</v>
+      </c>
+      <c r="K43" t="s">
+        <v>23</v>
+      </c>
+      <c r="L43" t="s">
+        <v>268</v>
+      </c>
+      <c r="M43" t="s">
+        <v>269</v>
+      </c>
+    </row>
+    <row r="44" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A44" t="s">
+        <v>270</v>
+      </c>
+      <c r="B44" t="s">
+        <v>271</v>
+      </c>
+      <c r="C44" t="s">
+        <v>15</v>
+      </c>
+      <c r="D44" t="s">
+        <v>272</v>
+      </c>
+      <c r="E44" t="s">
+        <v>228</v>
+      </c>
+      <c r="F44" t="s">
+        <v>18</v>
+      </c>
+      <c r="G44" t="s">
+        <v>19</v>
+      </c>
+      <c r="H44" t="s">
+        <v>20</v>
+      </c>
+      <c r="I44" t="s">
+        <v>21</v>
+      </c>
+      <c r="J44" t="s">
+        <v>20</v>
+      </c>
+      <c r="K44" t="s">
+        <v>23</v>
+      </c>
+      <c r="L44" t="s">
+        <v>273</v>
+      </c>
+      <c r="M44" t="s">
+        <v>274</v>
+      </c>
+    </row>
+    <row r="45" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A45" t="s">
+        <v>275</v>
+      </c>
+      <c r="B45" t="s">
+        <v>276</v>
+      </c>
+      <c r="C45" t="s">
+        <v>15</v>
+      </c>
+      <c r="D45" t="s">
+        <v>277</v>
+      </c>
+      <c r="E45" t="s">
+        <v>228</v>
+      </c>
+      <c r="F45" t="s">
+        <v>18</v>
+      </c>
+      <c r="G45" t="s">
+        <v>19</v>
+      </c>
+      <c r="H45" t="s">
+        <v>35</v>
+      </c>
+      <c r="I45" t="s">
+        <v>36</v>
+      </c>
+      <c r="J45" t="s">
+        <v>20</v>
+      </c>
+      <c r="K45" t="s">
+        <v>23</v>
+      </c>
+      <c r="L45" t="s">
+        <v>278</v>
+      </c>
+      <c r="M45" t="s">
+        <v>279</v>
+      </c>
+    </row>
+    <row r="46" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A46" t="s">
+        <v>280</v>
+      </c>
+      <c r="B46" t="s">
+        <v>281</v>
+      </c>
+      <c r="C46" t="s">
+        <v>15</v>
+      </c>
+      <c r="D46" t="s">
+        <v>282</v>
+      </c>
+      <c r="E46" t="s">
+        <v>228</v>
+      </c>
+      <c r="F46" t="s">
+        <v>18</v>
+      </c>
+      <c r="G46" t="s">
+        <v>19</v>
+      </c>
+      <c r="H46" t="s">
+        <v>35</v>
+      </c>
+      <c r="I46" t="s">
+        <v>36</v>
+      </c>
+      <c r="J46" t="s">
+        <v>90</v>
+      </c>
+      <c r="K46" t="s">
+        <v>23</v>
+      </c>
+      <c r="L46" t="s">
+        <v>283</v>
+      </c>
+      <c r="M46" t="s">
+        <v>284</v>
+      </c>
+    </row>
+    <row r="47" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A47" t="s">
+        <v>285</v>
+      </c>
+      <c r="B47" t="s">
+        <v>286</v>
+      </c>
+      <c r="C47" t="s">
+        <v>15</v>
+      </c>
+      <c r="D47" t="s">
+        <v>287</v>
+      </c>
+      <c r="E47" t="s">
+        <v>228</v>
+      </c>
+      <c r="F47" t="s">
+        <v>18</v>
+      </c>
+      <c r="G47" t="s">
+        <v>19</v>
+      </c>
+      <c r="H47" t="s">
+        <v>288</v>
+      </c>
+      <c r="I47" t="s">
+        <v>36</v>
+      </c>
+      <c r="J47" t="s">
+        <v>20</v>
+      </c>
+      <c r="K47" t="s">
+        <v>23</v>
+      </c>
+      <c r="L47" t="s">
+        <v>289</v>
+      </c>
+      <c r="M47" t="s">
+        <v>290</v>
+      </c>
+    </row>
+    <row r="48" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A48" t="s">
+        <v>291</v>
+      </c>
+      <c r="B48" t="s">
+        <v>292</v>
+      </c>
+      <c r="C48" t="s">
+        <v>293</v>
+      </c>
+      <c r="D48" t="s">
+        <v>294</v>
+      </c>
+      <c r="E48" t="s">
+        <v>228</v>
+      </c>
+      <c r="F48" t="s">
+        <v>18</v>
+      </c>
+      <c r="G48" t="s">
+        <v>19</v>
+      </c>
+      <c r="H48" t="s">
+        <v>20</v>
+      </c>
+      <c r="I48" t="s">
+        <v>21</v>
+      </c>
+      <c r="J48" t="s">
+        <v>20</v>
+      </c>
+      <c r="K48" t="s">
+        <v>23</v>
+      </c>
+      <c r="L48" t="s">
+        <v>295</v>
+      </c>
+      <c r="M48" t="s">
+        <v>296</v>
+      </c>
+    </row>
+    <row r="49" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A49" t="s">
+        <v>297</v>
+      </c>
+      <c r="B49" t="s">
+        <v>298</v>
+      </c>
+      <c r="C49" t="s">
+        <v>15</v>
+      </c>
+      <c r="D49" t="s">
+        <v>299</v>
+      </c>
+      <c r="E49" t="s">
+        <v>228</v>
+      </c>
+      <c r="F49" t="s">
+        <v>18</v>
+      </c>
+      <c r="G49" t="s">
+        <v>19</v>
+      </c>
+      <c r="H49" t="s">
+        <v>20</v>
+      </c>
+      <c r="I49" t="s">
+        <v>21</v>
+      </c>
+      <c r="J49" t="s">
+        <v>20</v>
+      </c>
+      <c r="K49" t="s">
+        <v>23</v>
+      </c>
+      <c r="L49" t="s">
+        <v>300</v>
+      </c>
+      <c r="M49" t="s">
+        <v>301</v>
+      </c>
+    </row>
+    <row r="50" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A50" t="s">
+        <v>302</v>
+      </c>
+      <c r="B50" t="s">
+        <v>303</v>
+      </c>
+      <c r="C50" t="s">
+        <v>15</v>
+      </c>
+      <c r="D50" t="s">
+        <v>304</v>
+      </c>
+      <c r="E50" t="s">
+        <v>228</v>
+      </c>
+      <c r="F50" t="s">
+        <v>18</v>
+      </c>
+      <c r="G50" t="s">
+        <v>19</v>
+      </c>
+      <c r="H50" t="s">
+        <v>20</v>
+      </c>
+      <c r="I50" t="s">
+        <v>21</v>
+      </c>
+      <c r="J50" t="s">
+        <v>90</v>
+      </c>
+      <c r="K50" t="s">
+        <v>23</v>
+      </c>
+      <c r="L50" t="s">
+        <v>305</v>
+      </c>
+      <c r="M50" t="s">
+        <v>306</v>
+      </c>
+    </row>
+    <row r="51" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A51" t="s">
+        <v>307</v>
+      </c>
+      <c r="B51" t="s">
+        <v>308</v>
+      </c>
+      <c r="C51" t="s">
+        <v>46</v>
+      </c>
+      <c r="D51" t="s">
+        <v>309</v>
+      </c>
+      <c r="E51" t="s">
+        <v>310</v>
+      </c>
+      <c r="F51" t="s">
+        <v>18</v>
+      </c>
+      <c r="G51" t="s">
+        <v>19</v>
+      </c>
+      <c r="H51" t="s">
+        <v>35</v>
+      </c>
+      <c r="I51" t="s">
+        <v>36</v>
+      </c>
+      <c r="J51" t="s">
+        <v>20</v>
+      </c>
+      <c r="K51" t="s">
+        <v>23</v>
+      </c>
+      <c r="L51" t="s">
+        <v>311</v>
+      </c>
+      <c r="M51" t="s">
+        <v>312</v>
+      </c>
+    </row>
+    <row r="52" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A52" t="s">
+        <v>313</v>
+      </c>
+      <c r="B52" t="s">
+        <v>314</v>
+      </c>
+      <c r="C52" t="s">
+        <v>46</v>
+      </c>
+      <c r="D52" t="s">
+        <v>315</v>
+      </c>
+      <c r="E52" t="s">
+        <v>228</v>
+      </c>
+      <c r="F52" t="s">
+        <v>18</v>
+      </c>
+      <c r="G52" t="s">
+        <v>19</v>
+      </c>
+      <c r="H52" t="s">
+        <v>20</v>
+      </c>
+      <c r="I52" t="s">
+        <v>21</v>
+      </c>
+      <c r="J52" t="s">
+        <v>20</v>
+      </c>
+      <c r="K52" t="s">
+        <v>23</v>
+      </c>
+      <c r="L52" t="s">
+        <v>316</v>
+      </c>
+      <c r="M52" t="s">
+        <v>317</v>
+      </c>
+    </row>
+    <row r="53" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A53" t="s">
+        <v>318</v>
+      </c>
+      <c r="B53" t="s">
+        <v>319</v>
+      </c>
+      <c r="C53" t="s">
+        <v>320</v>
+      </c>
+      <c r="D53" t="s">
+        <v>321</v>
+      </c>
+      <c r="E53" t="s">
+        <v>228</v>
+      </c>
+      <c r="F53" t="s">
+        <v>18</v>
+      </c>
+      <c r="G53" t="s">
+        <v>19</v>
+      </c>
+      <c r="H53" t="s">
+        <v>20</v>
+      </c>
+      <c r="I53" t="s">
+        <v>21</v>
+      </c>
+      <c r="J53" t="s">
+        <v>20</v>
+      </c>
+      <c r="K53" t="s">
+        <v>23</v>
+      </c>
+      <c r="L53" t="s">
+        <v>322</v>
+      </c>
+      <c r="M53" t="s">
+        <v>323</v>
+      </c>
+    </row>
+    <row r="54" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A54" t="s">
+        <v>324</v>
+      </c>
+      <c r="B54" t="s">
+        <v>325</v>
+      </c>
+      <c r="C54" t="s">
+        <v>127</v>
+      </c>
+      <c r="D54" t="s">
+        <v>326</v>
+      </c>
+      <c r="E54" t="s">
+        <v>228</v>
+      </c>
+      <c r="F54" t="s">
+        <v>18</v>
+      </c>
+      <c r="G54" t="s">
+        <v>19</v>
+      </c>
+      <c r="H54" t="s">
+        <v>20</v>
+      </c>
+      <c r="I54" t="s">
+        <v>21</v>
+      </c>
+      <c r="J54" t="s">
+        <v>20</v>
+      </c>
+      <c r="K54" t="s">
+        <v>23</v>
+      </c>
+      <c r="L54" t="s">
+        <v>327</v>
+      </c>
+      <c r="M54" t="s">
+        <v>328</v>
+      </c>
+    </row>
+    <row r="55" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A55" t="s">
+        <v>329</v>
+      </c>
+      <c r="B55" t="s">
+        <v>330</v>
+      </c>
+      <c r="C55" t="s">
+        <v>28</v>
+      </c>
+      <c r="D55" t="s">
+        <v>331</v>
+      </c>
+      <c r="E55" t="s">
+        <v>332</v>
+      </c>
+      <c r="F55" t="s">
+        <v>18</v>
+      </c>
+      <c r="G55" t="s">
+        <v>19</v>
+      </c>
+      <c r="H55" t="s">
+        <v>20</v>
+      </c>
+      <c r="I55" t="s">
+        <v>21</v>
+      </c>
+      <c r="J55" t="s">
+        <v>20</v>
+      </c>
+      <c r="K55" t="s">
+        <v>23</v>
+      </c>
+      <c r="L55" t="s">
+        <v>333</v>
+      </c>
+      <c r="M55" t="s">
+        <v>334</v>
+      </c>
+    </row>
+    <row r="56" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A56" t="s">
+        <v>335</v>
+      </c>
+      <c r="B56" t="s">
+        <v>336</v>
+      </c>
+      <c r="C56" t="s">
+        <v>15</v>
+      </c>
+      <c r="D56" t="s">
+        <v>337</v>
+      </c>
+      <c r="E56" t="s">
+        <v>17</v>
+      </c>
+      <c r="F56" t="s">
+        <v>18</v>
+      </c>
+      <c r="G56" t="s">
+        <v>19</v>
+      </c>
+      <c r="H56" t="s">
+        <v>35</v>
+      </c>
+      <c r="I56" t="s">
+        <v>36</v>
+      </c>
+      <c r="J56" t="s">
+        <v>20</v>
+      </c>
+      <c r="K56" t="s">
+        <v>23</v>
+      </c>
+      <c r="L56" t="s">
+        <v>338</v>
+      </c>
+      <c r="M56" t="s">
+        <v>339</v>
+      </c>
+    </row>
+    <row r="57" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A57" t="s">
+        <v>340</v>
+      </c>
+      <c r="B57" t="s">
+        <v>341</v>
+      </c>
+      <c r="C57" t="s">
+        <v>15</v>
+      </c>
+      <c r="D57" t="s">
+        <v>342</v>
+      </c>
+      <c r="E57" t="s">
+        <v>332</v>
+      </c>
+      <c r="F57" t="s">
+        <v>18</v>
+      </c>
+      <c r="G57" t="s">
+        <v>19</v>
+      </c>
+      <c r="H57" t="s">
+        <v>35</v>
+      </c>
+      <c r="I57" t="s">
+        <v>36</v>
+      </c>
+      <c r="J57" t="s">
+        <v>90</v>
+      </c>
+      <c r="K57" t="s">
+        <v>23</v>
+      </c>
+      <c r="L57" t="s">
+        <v>343</v>
+      </c>
+      <c r="M57" t="s">
+        <v>344</v>
+      </c>
+    </row>
+    <row r="58" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A58" t="s">
+        <v>345</v>
+      </c>
+      <c r="B58" t="s">
+        <v>346</v>
+      </c>
+      <c r="C58" t="s">
+        <v>15</v>
+      </c>
+      <c r="D58" t="s">
+        <v>347</v>
+      </c>
+      <c r="E58" t="s">
+        <v>332</v>
+      </c>
+      <c r="F58" t="s">
+        <v>18</v>
+      </c>
+      <c r="G58" t="s">
+        <v>19</v>
+      </c>
+      <c r="H58" t="s">
+        <v>35</v>
+      </c>
+      <c r="I58" t="s">
+        <v>36</v>
+      </c>
+      <c r="J58" t="s">
+        <v>20</v>
+      </c>
+      <c r="K58" t="s">
+        <v>23</v>
+      </c>
+      <c r="L58" t="s">
+        <v>348</v>
+      </c>
+      <c r="M58" t="s">
+        <v>349</v>
+      </c>
+    </row>
+    <row r="59" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A59" t="s">
+        <v>350</v>
+      </c>
+      <c r="B59" t="s">
+        <v>351</v>
+      </c>
+      <c r="C59" t="s">
+        <v>15</v>
+      </c>
+      <c r="D59" t="s">
+        <v>352</v>
+      </c>
+      <c r="E59" t="s">
+        <v>17</v>
+      </c>
+      <c r="F59" t="s">
+        <v>18</v>
+      </c>
+      <c r="G59" t="s">
+        <v>19</v>
+      </c>
+      <c r="H59" t="s">
+        <v>35</v>
+      </c>
+      <c r="I59" t="s">
+        <v>36</v>
+      </c>
+      <c r="J59" t="s">
+        <v>20</v>
+      </c>
+      <c r="K59" t="s">
+        <v>23</v>
+      </c>
+      <c r="L59" t="s">
+        <v>353</v>
+      </c>
+      <c r="M59" t="s">
+        <v>354</v>
+      </c>
+    </row>
+    <row r="60" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A60" t="s">
+        <v>355</v>
+      </c>
+      <c r="B60" t="s">
+        <v>356</v>
+      </c>
+      <c r="C60" t="s">
+        <v>357</v>
+      </c>
+      <c r="D60" t="s">
+        <v>358</v>
+      </c>
+      <c r="E60" t="s">
+        <v>332</v>
+      </c>
+      <c r="F60" t="s">
+        <v>18</v>
+      </c>
+      <c r="G60" t="s">
+        <v>19</v>
+      </c>
+      <c r="H60" t="s">
+        <v>166</v>
+      </c>
+      <c r="I60" t="s">
+        <v>36</v>
+      </c>
+      <c r="J60" t="s">
+        <v>359</v>
+      </c>
+      <c r="K60" t="s">
+        <v>23</v>
+      </c>
+      <c r="L60" t="s">
+        <v>360</v>
+      </c>
+      <c r="M60" t="s">
+        <v>361</v>
+      </c>
+    </row>
+    <row r="61" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A61" t="s">
+        <v>362</v>
+      </c>
+      <c r="B61" t="s">
+        <v>363</v>
+      </c>
+      <c r="C61" t="s">
+        <v>46</v>
+      </c>
+      <c r="D61" t="s">
+        <v>364</v>
+      </c>
+      <c r="E61" t="s">
+        <v>365</v>
+      </c>
+      <c r="F61" t="s">
+        <v>18</v>
+      </c>
+      <c r="G61" t="s">
+        <v>19</v>
+      </c>
+      <c r="H61" t="s">
+        <v>20</v>
+      </c>
+      <c r="I61" t="s">
+        <v>21</v>
+      </c>
+      <c r="J61" t="s">
+        <v>20</v>
+      </c>
+      <c r="K61" t="s">
+        <v>23</v>
+      </c>
+      <c r="L61" t="s">
+        <v>366</v>
+      </c>
+      <c r="M61" t="s">
+        <v>367</v>
+      </c>
+    </row>
+    <row r="62" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A62" t="s">
+        <v>368</v>
+      </c>
+      <c r="B62" t="s">
+        <v>369</v>
+      </c>
+      <c r="C62" t="s">
+        <v>46</v>
+      </c>
+      <c r="D62" t="s">
+        <v>370</v>
+      </c>
+      <c r="E62" t="s">
+        <v>371</v>
+      </c>
+      <c r="F62" t="s">
+        <v>18</v>
+      </c>
+      <c r="G62" t="s">
+        <v>19</v>
+      </c>
+      <c r="H62" t="s">
+        <v>20</v>
+      </c>
+      <c r="I62" t="s">
+        <v>21</v>
+      </c>
+      <c r="J62" t="s">
+        <v>20</v>
+      </c>
+      <c r="K62" t="s">
+        <v>23</v>
+      </c>
+      <c r="L62" t="s">
+        <v>372</v>
+      </c>
+      <c r="M62" t="s">
+        <v>373</v>
+      </c>
+    </row>
+    <row r="63" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A63" t="s">
+        <v>374</v>
+      </c>
+      <c r="B63" t="s">
+        <v>375</v>
+      </c>
+      <c r="C63" t="s">
+        <v>46</v>
+      </c>
+      <c r="D63" t="s">
+        <v>376</v>
+      </c>
+      <c r="E63" t="s">
+        <v>17</v>
+      </c>
+      <c r="F63" t="s">
+        <v>18</v>
+      </c>
+      <c r="G63" t="s">
+        <v>19</v>
+      </c>
+      <c r="H63" t="s">
+        <v>20</v>
+      </c>
+      <c r="I63" t="s">
+        <v>21</v>
+      </c>
+      <c r="J63" t="s">
+        <v>20</v>
+      </c>
+      <c r="K63" t="s">
+        <v>23</v>
+      </c>
+      <c r="L63" t="s">
+        <v>377</v>
+      </c>
+      <c r="M63" t="s">
+        <v>378</v>
+      </c>
+    </row>
+    <row r="64" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A64" t="s">
+        <v>379</v>
+      </c>
+      <c r="B64" t="s">
+        <v>380</v>
+      </c>
+      <c r="C64" t="s">
+        <v>46</v>
+      </c>
+      <c r="D64" t="s">
+        <v>381</v>
+      </c>
+      <c r="E64" t="s">
+        <v>382</v>
+      </c>
+      <c r="F64" t="s">
+        <v>18</v>
+      </c>
+      <c r="G64" t="s">
+        <v>19</v>
+      </c>
+      <c r="H64" t="s">
+        <v>20</v>
+      </c>
+      <c r="I64" t="s">
+        <v>21</v>
+      </c>
+      <c r="J64" t="s">
+        <v>20</v>
+      </c>
+      <c r="K64" t="s">
+        <v>23</v>
+      </c>
+      <c r="L64" t="s">
+        <v>383</v>
+      </c>
+      <c r="M64" t="s">
+        <v>384</v>
+      </c>
+    </row>
+    <row r="65" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A65" t="s">
+        <v>385</v>
+      </c>
+      <c r="B65" t="s">
+        <v>386</v>
+      </c>
+      <c r="C65" t="s">
+        <v>15</v>
+      </c>
+      <c r="D65" t="s">
+        <v>387</v>
+      </c>
+      <c r="E65" t="s">
+        <v>332</v>
+      </c>
+      <c r="F65" t="s">
+        <v>18</v>
+      </c>
+      <c r="G65" t="s">
+        <v>19</v>
+      </c>
+      <c r="H65" t="s">
+        <v>388</v>
+      </c>
+      <c r="I65" t="s">
+        <v>36</v>
+      </c>
+      <c r="J65" t="s">
+        <v>20</v>
+      </c>
+      <c r="K65" t="s">
+        <v>23</v>
+      </c>
+      <c r="L65" t="s">
+        <v>389</v>
+      </c>
+      <c r="M65" t="s">
+        <v>390</v>
+      </c>
+    </row>
+    <row r="66" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A66" t="s">
+        <v>391</v>
+      </c>
+      <c r="B66" t="s">
+        <v>392</v>
+      </c>
+      <c r="C66" t="s">
+        <v>15</v>
+      </c>
+      <c r="D66" t="s">
+        <v>393</v>
+      </c>
+      <c r="E66" t="s">
+        <v>332</v>
+      </c>
+      <c r="F66" t="s">
+        <v>18</v>
+      </c>
+      <c r="G66" t="s">
+        <v>19</v>
+      </c>
+      <c r="H66" t="s">
+        <v>20</v>
+      </c>
+      <c r="I66" t="s">
+        <v>21</v>
+      </c>
+      <c r="J66" t="s">
+        <v>20</v>
+      </c>
+      <c r="K66" t="s">
+        <v>23</v>
+      </c>
+      <c r="L66" t="s">
+        <v>394</v>
+      </c>
+      <c r="M66" t="s">
+        <v>395</v>
+      </c>
+    </row>
+    <row r="67" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A67" t="s">
+        <v>396</v>
+      </c>
+      <c r="B67" t="s">
+        <v>397</v>
+      </c>
+      <c r="C67" t="s">
+        <v>15</v>
+      </c>
+      <c r="D67" t="s">
+        <v>398</v>
+      </c>
+      <c r="E67" t="s">
+        <v>399</v>
+      </c>
+      <c r="F67" t="s">
+        <v>18</v>
+      </c>
+      <c r="G67" t="s">
+        <v>19</v>
+      </c>
+      <c r="H67" t="s">
+        <v>211</v>
+      </c>
+      <c r="I67" t="s">
+        <v>36</v>
+      </c>
+      <c r="J67" t="s">
+        <v>20</v>
+      </c>
+      <c r="K67" t="s">
+        <v>23</v>
+      </c>
+      <c r="L67" t="s">
+        <v>400</v>
+      </c>
+      <c r="M67" t="s">
+        <v>401</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>

--- a/Sajjad data/by_country_and_state/USA/MN.xlsx
+++ b/Sajjad data/by_country_and_state/USA/MN.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="871" uniqueCount="402">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="884" uniqueCount="409">
   <si>
     <t>Business Name</t>
   </si>
@@ -1217,6 +1217,27 @@
   </si>
   <si>
     <t>2026-10-25T09:15:20.871Z</t>
+  </si>
+  <si>
+    <t>Steidl Family Dentistry, PC</t>
+  </si>
+  <si>
+    <t>(218) 236-9319</t>
+  </si>
+  <si>
+    <t>915 37 Ave S, Moorhead, MN 56560</t>
+  </si>
+  <si>
+    <t>Moorhead</t>
+  </si>
+  <si>
+    <t>4.3</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/Steidl+Family+Dentistry,+PC/data=!4m7!3m6!1s0x52c8ce944e6f9699:0x97575cdd09bef467!8m2!3d46.8360361!4d-96.7656001!16s%2Fg%2F1vd94rfd!19sChIJmZZvTpTOyFIRZ_S-Cd1cV5c?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>2026-10-25T22:24:48.275Z</t>
   </si>
 </sst>
 </file>
@@ -1597,7 +1618,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:M67"/>
+  <dimension ref="A1:M68"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="34" customWidth="1"/>
@@ -4361,6 +4382,47 @@
         <v>401</v>
       </c>
     </row>
+    <row r="68" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A68" t="s">
+        <v>402</v>
+      </c>
+      <c r="B68" t="s">
+        <v>403</v>
+      </c>
+      <c r="C68" t="s">
+        <v>15</v>
+      </c>
+      <c r="D68" t="s">
+        <v>404</v>
+      </c>
+      <c r="E68" t="s">
+        <v>405</v>
+      </c>
+      <c r="F68" t="s">
+        <v>18</v>
+      </c>
+      <c r="G68" t="s">
+        <v>19</v>
+      </c>
+      <c r="H68" t="s">
+        <v>406</v>
+      </c>
+      <c r="I68" t="s">
+        <v>36</v>
+      </c>
+      <c r="J68" t="s">
+        <v>90</v>
+      </c>
+      <c r="K68" t="s">
+        <v>23</v>
+      </c>
+      <c r="L68" t="s">
+        <v>407</v>
+      </c>
+      <c r="M68" t="s">
+        <v>408</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
